--- a/testdata/RFQ.xlsx
+++ b/testdata/RFQ.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15990" windowHeight="6540" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15990" windowHeight="6540" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Supplier1" sheetId="2" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet name="Domestic" sheetId="4" r:id="rId3"/>
     <sheet name="Import" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="125725"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="58">
   <si>
     <t>Item Id</t>
   </si>
@@ -198,6 +198,12 @@
   </si>
   <si>
     <t>Import2</t>
+  </si>
+  <si>
+    <t>ROAU-RFQ-KDK-01</t>
+  </si>
+  <si>
+    <t>ROAU-RFQ-KDK-02</t>
   </si>
 </sst>
 </file>
@@ -1355,7 +1361,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="C4" s="22" t="s">
         <v>18</v>
@@ -1445,7 +1451,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>18</v>
@@ -1698,7 +1704,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="C12" s="22" t="s">
         <v>20</v>
@@ -1788,7 +1794,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="C13" s="22" t="s">
         <v>20</v>
@@ -2083,7 +2089,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="C4" s="22" t="s">
         <v>54</v>
@@ -2173,7 +2179,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>54</v>
@@ -2451,7 +2457,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="C12" s="22" t="s">
         <v>18</v>
@@ -2541,7 +2547,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="C13" s="22" t="s">
         <v>18</v>
